--- a/artfynd/A 26633-2019 artfynd.xlsx
+++ b/artfynd/A 26633-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 26633-2019 artfynd.xlsx
+++ b/artfynd/A 26633-2019 artfynd.xlsx
@@ -1324,7 +1324,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119872376</v>
+        <v>119873061</v>
       </c>
       <c r="B7" t="n">
         <v>4652</v>
@@ -1365,14 +1365,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Haningsbäcken, Haningsbäcken, Ång</t>
+          <t>Höån, Höån, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>611884</v>
+        <v>611947</v>
       </c>
       <c r="R7" t="n">
-        <v>6981629</v>
+        <v>6981506</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1431,7 +1431,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119873061</v>
+        <v>119872376</v>
       </c>
       <c r="B8" t="n">
         <v>4652</v>
@@ -1472,14 +1472,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Höån, Höån, Ång</t>
+          <t>Haningsbäcken, Haningsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>611947</v>
+        <v>611884</v>
       </c>
       <c r="R8" t="n">
-        <v>6981506</v>
+        <v>6981629</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>

--- a/artfynd/A 26633-2019 artfynd.xlsx
+++ b/artfynd/A 26633-2019 artfynd.xlsx
@@ -1324,7 +1324,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119873061</v>
+        <v>119872376</v>
       </c>
       <c r="B7" t="n">
         <v>4652</v>
@@ -1365,14 +1365,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Höån, Höån, Ång</t>
+          <t>Haningsbäcken, Haningsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>611947</v>
+        <v>611884</v>
       </c>
       <c r="R7" t="n">
-        <v>6981506</v>
+        <v>6981629</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1431,7 +1431,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119872376</v>
+        <v>119873061</v>
       </c>
       <c r="B8" t="n">
         <v>4652</v>
@@ -1472,14 +1472,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Haningsbäcken, Haningsbäcken, Ång</t>
+          <t>Höån, Höån, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>611884</v>
+        <v>611947</v>
       </c>
       <c r="R8" t="n">
-        <v>6981629</v>
+        <v>6981506</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
